--- a/data/availability/projects/palm-hills-developments/hacienda-blue.xlsx
+++ b/data/availability/projects/palm-hills-developments/hacienda-blue.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Template for Hacienda Blue</t>
+          <t>Live inventory for hacienda-blue</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,6 +543,106 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>payment_plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>278</v>
+      </c>
+      <c r="F2" t="n">
+        <v>278</v>
+      </c>
+      <c r="G2" t="n">
+        <v>69.62</v>
+      </c>
+      <c r="H2" t="n">
+        <v>69.62</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3" t="n">
+        <v>114</v>
+      </c>
+      <c r="F3" t="n">
+        <v>164</v>
+      </c>
+      <c r="G3" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="H3" t="n">
+        <v>30.07</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
         </is>
       </c>
     </row>
@@ -557,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,6 +727,1292 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HBLU-VLB-321</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>278</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>69620000</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HBLU-VLB-331</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>278</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>69620000</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>HBLU-SCH-304BF</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>154</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>27619000</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HBLU-SCH-304BG</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>164</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Garden: 209.5 sqm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>30070000</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HBLU-SCH-402AF</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>154</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>28135000</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>HBLU-SCH-402BF</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>154</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>28135000</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HBLU-SCH-403AF</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>154</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>28135000</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HBLU-SCH-403BF</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>154</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>28135000</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HBLU-SCH-450BF</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>154</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>28135000</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HBLU-SCH-601AF</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>154</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>27619000</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HBLU-SCH-601AG</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>164</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Garden: 209.5 sqm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>30069000</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HBLU-SCH-601BF</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>154</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>27619000</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HBLU-SCH-601BG</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>164</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Garden: 209.5 sqm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>30069000</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HBLU-SCH-602AF</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>154</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>27619000</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HBLU-SCH-602BF</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>154</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>27619000</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HBLU-SCH-602BG</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>164</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Garden: 209.5 sqm</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>30069000</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HBLU-JCH-604BF</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>114</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>23292000</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HBLU-SCH-608BF</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>154</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>27619000</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>HBLU-SCH-608BG</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>164</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Garden: 209.5 sqm</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>30069000</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>HBLU-JCH-612AG</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>116</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Garden: 186 sqm</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>25250000</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HBLU-JCH-612BG</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>116</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Garden: 186 sqm</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>25250000</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>hacienda-blue</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HBLU-JCH-617AG</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HBLU-Phase 1</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>116</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Garden: 186 sqm</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>25250000</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/availability/projects/palm-hills-developments/hacienda-blue.xlsx
+++ b/data/availability/projects/palm-hills-developments/hacienda-blue.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -709,7 +709,6 @@
       <c r="G2" t="n">
         <v>154.5</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -720,7 +719,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -766,7 +765,6 @@
       <c r="G3" t="n">
         <v>154.5</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -777,7 +775,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -823,7 +821,6 @@
       <c r="G4" t="n">
         <v>154.5</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -834,7 +831,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -880,7 +877,6 @@
       <c r="G5" t="n">
         <v>154.5</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -891,7 +887,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -937,7 +933,6 @@
       <c r="G6" t="n">
         <v>154.5</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -948,7 +943,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -994,7 +989,6 @@
       <c r="G7" t="n">
         <v>154.5</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1005,7 +999,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1051,7 +1045,6 @@
       <c r="G8" t="n">
         <v>154.5</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1062,7 +1055,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1108,7 +1101,6 @@
       <c r="G9" t="n">
         <v>154.5</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1119,7 +1111,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1165,7 +1157,6 @@
       <c r="G10" t="n">
         <v>164</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1176,7 +1167,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1222,7 +1213,6 @@
       <c r="G11" t="n">
         <v>154.5</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1233,7 +1223,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1279,7 +1269,6 @@
       <c r="G12" t="n">
         <v>154.5</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1290,7 +1279,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1336,7 +1325,6 @@
       <c r="G13" t="n">
         <v>164</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1347,7 +1335,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1393,7 +1381,6 @@
       <c r="G14" t="n">
         <v>114.5</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1404,7 +1391,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1450,7 +1437,6 @@
       <c r="G15" t="n">
         <v>154.5</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1461,7 +1447,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1507,7 +1493,6 @@
       <c r="G16" t="n">
         <v>164</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1518,7 +1503,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1564,7 +1549,6 @@
       <c r="G17" t="n">
         <v>116</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1575,7 +1559,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
